--- a/timetable.xlsx
+++ b/timetable.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Schedule" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Timetable" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -52,12 +52,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -429,9 +425,9 @@
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -440,249 +436,231 @@
           <t>Time</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Speaker</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">報到
-</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>09:00-09:30</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>報到</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>無</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>開場致詞
-王教授</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>09:30-09:40</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>開場致詞</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>王教授</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>從 MWC 2026 到 6G：AI-RAN 標準、開源與互通測試的最新進展
-劉教授</t>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>09:40-10:05</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>從 MWC 2026 到 6G：AI-RAN 標準、開源與互通測試的最新進展</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>劉教授</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>基於 O-RAN 開放介面的 ISAC 無線感知技術
-陳教授</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>10:05-10:30</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>基於 O-RAN 開放介面的 ISAC 無線感知技術</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>陳教授</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Break
-</t>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>10:30-10:50</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>無</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Federated Foundational Models in AI-RAN：Practical and Forward Looking Perspective
-教學團隊</t>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10:50-11:20</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Federated Foundational Models in AI-RAN：Practical and Forward Looking Perspective</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>教學團隊</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>O-RAN 環境與各模組化功能介紹
-教學團隊</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>11:20-12:00</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>O-RAN 環境與各模組化功能介紹</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lunch
-</t>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>12:00-13:30</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>無</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>O-RAN 開源軟體組織簡介
-教學團隊</t>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>13:30-14:00</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>O-RAN 開源軟體組織簡介</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>教學團隊</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>O-RAN 實驗環境建置教學
-教學團隊</t>
-        </is>
-      </c>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>14:00-14:30</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>O-RAN 實驗環境建置教學</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Break
-</t>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>14:30-14:50</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>無</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>O-RAN xApps 實作建置教學
-教學團隊</t>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>14:50-15:50</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>O-RAN xApps 實作建置教學</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>教學團隊</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>現場討論時間
-教學團隊</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>15:50-16:30</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>現場討論時間</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+  <mergeCells count="3">
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C10:C11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
